--- a/data/processed/harmonization/Base_cations__Exchangeable_magnesium/harmonized.xlsx
+++ b/data/processed/harmonization/Base_cations__Exchangeable_magnesium/harmonized.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="54" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -614,12 +614,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3:3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -662,12 +662,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4:4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -710,12 +710,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5:5</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -758,12 +758,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1:6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -806,12 +806,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2:7</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -854,12 +854,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3:8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -902,12 +902,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4:9</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -950,12 +950,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5:10</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -998,12 +998,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6:11</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8:12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>IEEXG001N</t>
+          <t>upland:IEEXG001N</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>IEEXG001Q</t>
+          <t>transition:IEEXG001Q</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>IEEXG001K</t>
+          <t>wetland:IEEXG001K</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003F</t>
+          <t>upland:IEEXG003F</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003I</t>
+          <t>transition:IEEXG003I</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003C</t>
+          <t>wetland:IEEXG003C</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003V</t>
+          <t>upland:IEEXG003V</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003Y</t>
+          <t>transition:IEEXG003Y</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003S</t>
+          <t>wetland:IEEXG003S</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004B</t>
+          <t>upland:IEEXG004B</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004E</t>
+          <t>transition:IEEXG004E</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0048</t>
+          <t>wetland:IEEXG0048</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004R</t>
+          <t>upland:IEEXG004R</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004U</t>
+          <t>transition:IEEXG004U</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1966,12 +1966,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004O</t>
+          <t>wetland:IEEXG004O</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0054</t>
+          <t>wetland:IEEXG0054</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>IEEXG005N</t>
+          <t>upland:IEEXG005N</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -2122,12 +2122,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>IEEXG005Q</t>
+          <t>transition:IEEXG005Q</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>IEEXG005K</t>
+          <t>wetland:IEEXG005K</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0060</t>
+          <t>wetland:IEEXG0060</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -2278,12 +2278,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006J</t>
+          <t>upland:IEEXG006J</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -2330,12 +2330,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006M</t>
+          <t>transition:IEEXG006M</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006G</t>
+          <t>wetland:IEEXG006G</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006Z</t>
+          <t>upland:IEEXG006Z</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0072</t>
+          <t>transition:IEEXG0072</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006W</t>
+          <t>wetland:IEEXG006W</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>IEEXG007F</t>
+          <t>upland:IEEXG007F</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -2642,12 +2642,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>IEEXG007I</t>
+          <t>transition:IEEXG007I</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2694,12 +2694,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>IEEXG007C</t>
+          <t>wetland:IEEXG007C</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2746,12 +2746,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>IEEXG008B</t>
+          <t>upland:IEEXG008B</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2798,12 +2798,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>IEEXG008E</t>
+          <t>transition:IEEXG008E</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2850,12 +2850,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0088</t>
+          <t>wetland:IEEXG0088</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>IEEXG008R</t>
+          <t>upland:IEEXG008R</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0097</t>
+          <t>upland:IEEXG0097</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>IEEXG009A</t>
+          <t>transition:IEEXG009A</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -3058,12 +3058,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0094</t>
+          <t>wetland:IEEXG0094</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>IEEXG009N</t>
+          <t>upland:IEEXG009N</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -3162,12 +3162,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>IEEXG009Q</t>
+          <t>transition:IEEXG009Q</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -3214,12 +3214,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>IEEXG009K</t>
+          <t>wetland:IEEXG009K</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00A3</t>
+          <t>upland:IEEXG00A3</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -3318,12 +3318,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00A0</t>
+          <t>wetland:IEEXG00A0</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00AJ</t>
+          <t>upland:IEEXG00AJ</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -3422,12 +3422,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00AM</t>
+          <t>transition:IEEXG00AM</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00AZ</t>
+          <t>upland:IEEXG00AZ</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -3526,12 +3526,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00B2</t>
+          <t>transition:IEEXG00B2</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00AW</t>
+          <t>wetland:IEEXG00AW</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -3630,12 +3630,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00BF</t>
+          <t>upland:IEEXG00BF</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00BI</t>
+          <t>transition:IEEXG00BI</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00BC</t>
+          <t>wetland:IEEXG00BC</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -3786,12 +3786,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00CR</t>
+          <t>upland:IEEXG00CR</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -3838,12 +3838,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00CU</t>
+          <t>transition:IEEXG00CU</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -3890,12 +3890,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00CO</t>
+          <t>wetland:IEEXG00CO</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00D7</t>
+          <t>upland:IEEXG00D7</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -3994,12 +3994,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00D4</t>
+          <t>wetland:IEEXG00D4</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -4046,12 +4046,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00EJ</t>
+          <t>upland:IEEXG00EJ</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -4098,12 +4098,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00EG</t>
+          <t>wetland:IEEXG00EG</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00EZ</t>
+          <t>upland:IEEXG00EZ</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -4202,12 +4202,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00F2</t>
+          <t>transition:IEEXG00F2</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00EW</t>
+          <t>wetland:IEEXG00EW</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FF</t>
+          <t>upland:IEEXG00FF</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FI</t>
+          <t>transition:IEEXG00FI</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -4410,12 +4410,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FC</t>
+          <t>wetland:IEEXG00FC</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -4462,12 +4462,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FV</t>
+          <t>upland:IEEXG00FV</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FY</t>
+          <t>transition:IEEXG00FY</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -4566,12 +4566,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FS</t>
+          <t>wetland:IEEXG00FS</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -4618,12 +4618,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00G8</t>
+          <t>wetland:IEEXG00G8</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -4670,12 +4670,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00GR</t>
+          <t>upland:IEEXG00GR</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -4722,12 +4722,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00GO</t>
+          <t>wetland:IEEXG00GO</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -4774,12 +4774,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00H7</t>
+          <t>upland:IEEXG00H7</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00HA</t>
+          <t>transition:IEEXG00HA</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -4878,12 +4878,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00H4</t>
+          <t>wetland:IEEXG00H4</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -4930,12 +4930,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00HN</t>
+          <t>upland:IEEXG00HN</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -4982,12 +4982,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00HQ</t>
+          <t>transition:IEEXG00HQ</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00HK</t>
+          <t>wetland:IEEXG00HK</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -5086,12 +5086,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00I3</t>
+          <t>upland:IEEXG00I3</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -5138,12 +5138,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00I6</t>
+          <t>transition:IEEXG00I6</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
@@ -5190,12 +5190,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00I0</t>
+          <t>wetland:IEEXG00I0</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
@@ -5242,12 +5242,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00IJ</t>
+          <t>upland:IEEXG00IJ</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00IM</t>
+          <t>transition:IEEXG00IM</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -5346,12 +5346,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00IG</t>
+          <t>wetland:IEEXG00IG</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JF</t>
+          <t>upland:IEEXG00JF</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -5450,12 +5450,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JI</t>
+          <t>transition:IEEXG00JI</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
@@ -5502,12 +5502,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JC</t>
+          <t>wetland:IEEXG00JC</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
@@ -5554,12 +5554,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JV</t>
+          <t>upland:IEEXG00JV</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -5606,12 +5606,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JY</t>
+          <t>transition:IEEXG00JY</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
@@ -5658,12 +5658,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JS</t>
+          <t>wetland:IEEXG00JS</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
@@ -5710,12 +5710,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00KB</t>
+          <t>upland:IEEXG00KB</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
@@ -5762,12 +5762,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00K8</t>
+          <t>wetland:IEEXG00K8</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
@@ -5814,12 +5814,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00KR</t>
+          <t>upland:IEEXG00KR</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -5866,12 +5866,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00KU</t>
+          <t>transition:IEEXG00KU</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -5918,12 +5918,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00KO</t>
+          <t>wetland:IEEXG00KO</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
@@ -5970,12 +5970,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00L7</t>
+          <t>upland:IEEXG00L7</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -6022,12 +6022,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00LA</t>
+          <t>transition:IEEXG00LA</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00L4</t>
+          <t>wetland:IEEXG00L4</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
@@ -6126,12 +6126,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00LN</t>
+          <t>upland:IEEXG00LN</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
@@ -6178,12 +6178,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00LQ</t>
+          <t>transition:IEEXG00LQ</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -6230,12 +6230,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00LK</t>
+          <t>wetland:IEEXG00LK</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -6282,12 +6282,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00M6</t>
+          <t>transition:IEEXG00M6</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -6334,12 +6334,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00M0</t>
+          <t>wetland:IEEXG00M0</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -6386,12 +6386,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00MJ</t>
+          <t>upland:IEEXG00MJ</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00MM</t>
+          <t>transition:IEEXG00MM</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
@@ -6490,12 +6490,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00MG</t>
+          <t>wetland:IEEXG00MG</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00MZ</t>
+          <t>upland:IEEXG00MZ</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -6594,12 +6594,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00N2</t>
+          <t>transition:IEEXG00N2</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NF</t>
+          <t>upland:IEEXG00NF</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -6698,12 +6698,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NI</t>
+          <t>transition:IEEXG00NI</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -6750,12 +6750,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NC</t>
+          <t>wetland:IEEXG00NC</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NV</t>
+          <t>upland:IEEXG00NV</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -6854,12 +6854,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NY</t>
+          <t>transition:IEEXG00NY</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -6906,12 +6906,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NS</t>
+          <t>wetland:IEEXG00NS</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -6958,12 +6958,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00OB</t>
+          <t>upland:IEEXG00OB</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00OR</t>
+          <t>upland:IEEXG00OR</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -7062,12 +7062,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00OU</t>
+          <t>transition:IEEXG00OU</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
@@ -7114,12 +7114,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00OO</t>
+          <t>wetland:IEEXG00OO</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -7166,12 +7166,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00PN</t>
+          <t>upland:IEEXG00PN</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00PQ</t>
+          <t>transition:IEEXG00PQ</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
@@ -7270,12 +7270,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00PK</t>
+          <t>wetland:IEEXG00PK</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
@@ -7322,12 +7322,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00Q3</t>
+          <t>upland:IEEXG00Q3</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00Q6</t>
+          <t>transition:IEEXG00Q6</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
@@ -7426,12 +7426,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00Q0</t>
+          <t>wetland:IEEXG00Q0</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
@@ -7478,12 +7478,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00QZ</t>
+          <t>upland:IEEXG00QZ</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00R2</t>
+          <t>transition:IEEXG00R2</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -7582,12 +7582,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00QW</t>
+          <t>wetland:IEEXG00QW</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
@@ -7634,12 +7634,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00RF</t>
+          <t>upland:IEEXG00RF</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
@@ -7686,12 +7686,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00RI</t>
+          <t>transition:IEEXG00RI</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr"/>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00RC</t>
+          <t>wetland:IEEXG00RC</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
